--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.127.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.127.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.127.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.127.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="41" customWidth="1" min="14" max="14"/>
-    <col width="35" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -605,28 +605,36 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L2: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: respondent respectively.â€” Provided</t>
+          <t>L131: stray/suspicious non-ASCII glyph(s): U+77FF CJK UNIFIED IDEOGRAPH-77FF | isolated marker/symbol line :: 矿</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L6: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: respondent respectively.â€”Provided always, that nothing</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]120</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]120</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L17: isolated marker/symbol line :: 120</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr"/>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]120</t>
+        </is>
+      </c>
       <c r="P2" s="1" t="inlineStr"/>
       <c r="Q2" s="1" t="inlineStr"/>
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L92: line starts with punctuation glued to text :: .absence, of t</t>
+          <t>L16: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •the Statute twelfth Victoria, Chapter sixty-three, Section</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -649,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -662,14 +670,10 @@
           <t>L94: suspicious token(s): the1 (letter/digit mix) | localized OCR phrase divergence vs other OCR: "the r" vs "the1" :: That the1</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L26: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ely.â€” Provided always, that nothing</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L16: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢the Statute twelfth Victoria, Chapter sixty-three, Section</t>
+          <t>L16: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •the Statute twelfth Victoria, Chapter sixty-three, Section</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -683,7 +687,11 @@
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr"/>
       <c r="R3" s="1" t="inlineStr"/>
-      <c r="S3" s="1" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>L27: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •costs and damages as shall be awarded in case the judg-</t>
+        </is>
+      </c>
       <c r="T3" s="1" t="inlineStr"/>
       <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr"/>
@@ -716,7 +724,7 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L27: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢costs and damages as shall be awarded in case the judg-</t>
+          <t>L27: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •costs and damages as shall be awarded in case the judg-</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -730,7 +738,11 @@
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr"/>
-      <c r="S4" s="1" t="inlineStr"/>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>L92: line starts with punctuation glued to text :: .absence, of t</t>
+        </is>
+      </c>
       <c r="T4" s="1" t="inlineStr"/>
       <c r="U4" s="1" t="inlineStr"/>
       <c r="V4" s="1" t="inlineStr"/>
@@ -746,12 +758,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -761,11 +773,7 @@
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L64: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: tyâ€™s Court of</t>
-        </is>
-      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -897,7 +905,11 @@
       <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
-      <c r="N8" s="1" t="inlineStr"/>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>L131: stray/suspicious non-ASCII glyph(s): U+77FF CJK UNIFIED IDEOGRAPH-77FF | isolated marker/symbol line :: 矿</t>
+        </is>
+      </c>
       <c r="O8" s="1" t="inlineStr"/>
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr"/>
@@ -957,12 +969,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1001,7 +1013,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1035,12 +1047,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1118,7 +1130,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
